--- a/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0001T0006Z000C1N6_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0001T0006Z000C1N6_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52.35303015812545</v>
+        <v>8.507367400695387</v>
       </c>
       <c r="D2" t="n">
-        <v>52.55959166987127</v>
+        <v>8.54093364635408</v>
       </c>
       <c r="E2" t="n">
-        <v>14.15933374995925</v>
+        <v>2.300891734368379</v>
       </c>
       <c r="F2" t="n">
-        <v>13.9938810214063</v>
+        <v>2.274005665978523</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.21780914836794</v>
+        <v>9.622893986609791</v>
       </c>
       <c r="D3" t="n">
-        <v>59.01084290461093</v>
+        <v>9.589261971999276</v>
       </c>
       <c r="E3" t="n">
-        <v>14.15933374995925</v>
+        <v>2.300891734368379</v>
       </c>
       <c r="F3" t="n">
-        <v>13.9938810214063</v>
+        <v>2.274005665978523</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.06741568881306</v>
+        <v>7.648455049432122</v>
       </c>
       <c r="D4" t="n">
-        <v>47.03523961363028</v>
+        <v>7.643226437214921</v>
       </c>
       <c r="E4" t="n">
-        <v>14.15933374995925</v>
+        <v>2.300891734368379</v>
       </c>
       <c r="F4" t="n">
-        <v>13.9938810214063</v>
+        <v>2.274005665978523</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.44860799848355</v>
+        <v>6.735398799753577</v>
       </c>
       <c r="D5" t="n">
-        <v>41.96860570219516</v>
+        <v>6.819898426606714</v>
       </c>
       <c r="E5" t="n">
-        <v>14.15933374995925</v>
+        <v>2.300891734368379</v>
       </c>
       <c r="F5" t="n">
-        <v>13.9938810214063</v>
+        <v>2.274005665978523</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>47.75956112530802</v>
+        <v>7.760928682862554</v>
       </c>
       <c r="D6" t="n">
-        <v>48.64297633091589</v>
+        <v>7.904483653773833</v>
       </c>
       <c r="E6" t="n">
-        <v>14.15933374995925</v>
+        <v>2.300891734368379</v>
       </c>
       <c r="F6" t="n">
-        <v>13.9938810214063</v>
+        <v>2.274005665978523</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>70.6482626110251</v>
+        <v>11.48034267429158</v>
       </c>
       <c r="D7" t="n">
-        <v>71.67478339935316</v>
+        <v>11.64715230239489</v>
       </c>
       <c r="E7" t="n">
-        <v>14.15933374995925</v>
+        <v>2.300891734368379</v>
       </c>
       <c r="F7" t="n">
-        <v>13.9938810214063</v>
+        <v>2.274005665978523</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>51.72236595194427</v>
+        <v>8.404884467190945</v>
       </c>
       <c r="D8" t="n">
-        <v>51.20493977886557</v>
+        <v>8.320802714065655</v>
       </c>
       <c r="E8" t="n">
-        <v>14.15933374995925</v>
+        <v>2.300891734368379</v>
       </c>
       <c r="F8" t="n">
-        <v>13.9938810214063</v>
+        <v>2.274005665978523</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.55023352127825</v>
+        <v>3.826912947207715</v>
       </c>
       <c r="D9" t="n">
-        <v>24.31699483810574</v>
+        <v>3.951511661192182</v>
       </c>
       <c r="E9" t="n">
-        <v>14.15933374995925</v>
+        <v>2.300891734368379</v>
       </c>
       <c r="F9" t="n">
-        <v>13.9938810214063</v>
+        <v>2.274005665978523</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>49.32547537150155</v>
+        <v>8.015389747869003</v>
       </c>
       <c r="D10" t="n">
-        <v>48.62303659416782</v>
+        <v>7.901243446552272</v>
       </c>
       <c r="E10" t="n">
-        <v>14.15933374995925</v>
+        <v>2.300891734368379</v>
       </c>
       <c r="F10" t="n">
-        <v>13.9938810214063</v>
+        <v>2.274005665978523</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>17.84127546079759</v>
+        <v>2.899207262379608</v>
       </c>
       <c r="D11" t="n">
-        <v>17.88755819339475</v>
+        <v>2.906728206426647</v>
       </c>
       <c r="E11" t="n">
-        <v>14.15933374995925</v>
+        <v>2.300891734368379</v>
       </c>
       <c r="F11" t="n">
-        <v>13.9938810214063</v>
+        <v>2.274005665978523</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>26.88499292150897</v>
+        <v>4.368811349745208</v>
       </c>
       <c r="D12" t="n">
-        <v>26.21377947333315</v>
+        <v>4.259739164416636</v>
       </c>
       <c r="E12" t="n">
-        <v>14.15933374995925</v>
+        <v>2.300891734368379</v>
       </c>
       <c r="F12" t="n">
-        <v>13.9938810214063</v>
+        <v>2.274005665978523</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>47.62277862209474</v>
+        <v>7.738701526090396</v>
       </c>
       <c r="D13" t="n">
-        <v>46.69570193609075</v>
+        <v>7.588051564614747</v>
       </c>
       <c r="E13" t="n">
-        <v>14.15933374995925</v>
+        <v>2.300891734368379</v>
       </c>
       <c r="F13" t="n">
-        <v>13.9938810214063</v>
+        <v>2.274005665978523</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>62.80613431133725</v>
+        <v>10.2059968255923</v>
       </c>
       <c r="D14" t="n">
-        <v>61.84790331457468</v>
+        <v>10.05028428861839</v>
       </c>
       <c r="E14" t="n">
-        <v>14.15933374995925</v>
+        <v>2.300891734368379</v>
       </c>
       <c r="F14" t="n">
-        <v>13.9938810214063</v>
+        <v>2.274005665978523</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>57.88905210840271</v>
+        <v>9.40697096761544</v>
       </c>
       <c r="D15" t="n">
-        <v>56.86099305297018</v>
+        <v>9.239911371107654</v>
       </c>
       <c r="E15" t="n">
-        <v>14.15933374995925</v>
+        <v>2.300891734368379</v>
       </c>
       <c r="F15" t="n">
-        <v>13.9938810214063</v>
+        <v>2.274005665978523</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>47.52167056162931</v>
+        <v>7.722271466264764</v>
       </c>
       <c r="D16" t="n">
-        <v>48.01432600216442</v>
+        <v>7.802327975351718</v>
       </c>
       <c r="E16" t="n">
-        <v>14.15933374995925</v>
+        <v>2.300891734368379</v>
       </c>
       <c r="F16" t="n">
-        <v>13.9938810214063</v>
+        <v>2.274005665978523</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>36.0029281285755</v>
+        <v>5.850475820893519</v>
       </c>
       <c r="D17" t="n">
-        <v>36.19864662493875</v>
+        <v>5.882280076552546</v>
       </c>
       <c r="E17" t="n">
-        <v>14.15933374995925</v>
+        <v>2.300891734368379</v>
       </c>
       <c r="F17" t="n">
-        <v>13.9938810214063</v>
+        <v>2.274005665978523</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>44.62976183162375</v>
+        <v>7.252336297638859</v>
       </c>
       <c r="D18" t="n">
-        <v>44.95939441016213</v>
+        <v>7.305901591651347</v>
       </c>
       <c r="E18" t="n">
-        <v>14.15933374995925</v>
+        <v>2.300891734368379</v>
       </c>
       <c r="F18" t="n">
-        <v>13.9938810214063</v>
+        <v>2.274005665978523</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>51.31767162885542</v>
+        <v>8.339121639689006</v>
       </c>
       <c r="D19" t="n">
-        <v>51.68393405053578</v>
+        <v>8.398639283212065</v>
       </c>
       <c r="E19" t="n">
-        <v>14.15933374995925</v>
+        <v>2.300891734368379</v>
       </c>
       <c r="F19" t="n">
-        <v>13.9938810214063</v>
+        <v>2.274005665978523</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>53.51875656271852</v>
+        <v>8.69679794144176</v>
       </c>
       <c r="D20" t="n">
-        <v>52.50314247212182</v>
+        <v>8.531760651719795</v>
       </c>
       <c r="E20" t="n">
-        <v>14.15933374995925</v>
+        <v>2.300891734368379</v>
       </c>
       <c r="F20" t="n">
-        <v>13.9938810214063</v>
+        <v>2.274005665978523</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>55.43732887199742</v>
+        <v>9.008565941699581</v>
       </c>
       <c r="D21" t="n">
-        <v>54.7120155572567</v>
+        <v>8.890702528054215</v>
       </c>
       <c r="E21" t="n">
-        <v>14.15933374995925</v>
+        <v>2.300891734368379</v>
       </c>
       <c r="F21" t="n">
-        <v>13.9938810214063</v>
+        <v>2.274005665978523</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>66.07032620156183</v>
+        <v>10.7364280077538</v>
       </c>
       <c r="D22" t="n">
-        <v>65.30376211865733</v>
+        <v>10.61186134428182</v>
       </c>
       <c r="E22" t="n">
-        <v>14.15933374995925</v>
+        <v>2.300891734368379</v>
       </c>
       <c r="F22" t="n">
-        <v>13.9938810214063</v>
+        <v>2.274005665978523</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>65.8693655401658</v>
+        <v>10.70377190027694</v>
       </c>
       <c r="D23" t="n">
-        <v>65.81981495001882</v>
+        <v>10.69571992937806</v>
       </c>
       <c r="E23" t="n">
-        <v>14.15933374995925</v>
+        <v>2.300891734368379</v>
       </c>
       <c r="F23" t="n">
-        <v>13.9938810214063</v>
+        <v>2.274005665978523</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>66.19088728815127</v>
+        <v>10.75601918432458</v>
       </c>
       <c r="D24" t="n">
-        <v>65.76768486353194</v>
+        <v>10.68724879032394</v>
       </c>
       <c r="E24" t="n">
-        <v>14.15933374995925</v>
+        <v>2.300891734368379</v>
       </c>
       <c r="F24" t="n">
-        <v>13.9938810214063</v>
+        <v>2.274005665978523</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>69.5877402127096</v>
+        <v>11.30800778456531</v>
       </c>
       <c r="D25" t="n">
-        <v>68.95808507372315</v>
+        <v>11.20568882448001</v>
       </c>
       <c r="E25" t="n">
-        <v>14.15933374995925</v>
+        <v>2.300891734368379</v>
       </c>
       <c r="F25" t="n">
-        <v>13.9938810214063</v>
+        <v>2.274005665978523</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>72.89509197223882</v>
+        <v>11.84545244548881</v>
       </c>
       <c r="D26" t="n">
-        <v>72.33914714146155</v>
+        <v>11.7551114104875</v>
       </c>
       <c r="E26" t="n">
-        <v>14.15933374995925</v>
+        <v>2.300891734368379</v>
       </c>
       <c r="F26" t="n">
-        <v>13.9938810214063</v>
+        <v>2.274005665978523</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
